--- a/diaries/Diari_annotati(25-07-25).xlsx
+++ b/diaries/Diari_annotati(25-07-25).xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10905"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sanraffaele-my.sharepoint.com/personal/manara_duilio_hsr_it/Documents/CERSI - FNOPI/LINGUAGGIO/Diari infermieristici/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/MacBook/B-Stuff/8-Lavoro/1-ISTAT/DCME/Lavoro_Mec/LLM/fnopi-classification/diaries/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1860" documentId="8_{B4C0B2B3-897C-474D-804C-48C1F4A6348D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EAC0C7AF-433D-4419-8493-69F057A19610}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19ED6246-82BC-0E42-B42A-0E0CE969C280}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="6380" yWindow="4500" windowWidth="32080" windowHeight="20640" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1420,7 +1420,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normale" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
@@ -1723,40 +1723,40 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A2:AC414"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="47.140625" style="5" customWidth="1"/>
-    <col min="2" max="2" width="9.7109375" style="6" customWidth="1"/>
-    <col min="3" max="3" width="10.85546875" style="6" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="16.28515625" style="6" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="21.5703125" style="7" customWidth="1"/>
-    <col min="6" max="6" width="20.85546875" style="6" customWidth="1"/>
-    <col min="7" max="7" width="20.85546875" style="7" customWidth="1"/>
-    <col min="8" max="8" width="21.5703125" style="6" customWidth="1"/>
-    <col min="9" max="9" width="20.85546875" style="7" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="24.42578125" style="6" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="20.85546875" style="7" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="20.85546875" style="6" customWidth="1"/>
-    <col min="13" max="13" width="20.85546875" style="7" customWidth="1"/>
-    <col min="14" max="14" width="20.85546875" style="6" customWidth="1"/>
-    <col min="15" max="15" width="20.85546875" style="7" customWidth="1"/>
-    <col min="16" max="16" width="20.85546875" style="6" customWidth="1"/>
-    <col min="17" max="17" width="20.85546875" style="7" customWidth="1"/>
-    <col min="18" max="18" width="20.85546875" style="6" customWidth="1"/>
-    <col min="19" max="19" width="20.85546875" style="7" customWidth="1"/>
-    <col min="20" max="20" width="20.85546875" style="6" customWidth="1"/>
-    <col min="21" max="21" width="20.85546875" style="7" customWidth="1"/>
-    <col min="22" max="22" width="20.85546875" style="6" customWidth="1"/>
-    <col min="23" max="23" width="20.85546875" style="7" customWidth="1"/>
-    <col min="24" max="24" width="20.85546875" style="6" customWidth="1"/>
-    <col min="25" max="25" width="20.85546875" style="7" customWidth="1"/>
-    <col min="26" max="26" width="20.7109375" style="6" customWidth="1"/>
-    <col min="27" max="27" width="20.7109375" style="7" customWidth="1"/>
-    <col min="28" max="28" width="20.7109375" style="6" customWidth="1"/>
-    <col min="29" max="29" width="20.7109375" style="7" customWidth="1"/>
+    <col min="1" max="1" width="59.83203125" style="5" customWidth="1"/>
+    <col min="2" max="2" width="9.6640625" style="6" customWidth="1"/>
+    <col min="3" max="3" width="10.83203125" style="6" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16.33203125" style="6" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="21.5" style="7" customWidth="1"/>
+    <col min="6" max="6" width="31.1640625" style="6" customWidth="1"/>
+    <col min="7" max="7" width="20.83203125" style="7" customWidth="1"/>
+    <col min="8" max="8" width="21.5" style="6" customWidth="1"/>
+    <col min="9" max="9" width="20.83203125" style="7" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="24.5" style="6" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="20.83203125" style="7" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="20.83203125" style="6" customWidth="1"/>
+    <col min="13" max="13" width="20.83203125" style="7" customWidth="1"/>
+    <col min="14" max="14" width="20.83203125" style="6" customWidth="1"/>
+    <col min="15" max="15" width="20.83203125" style="7" customWidth="1"/>
+    <col min="16" max="16" width="20.83203125" style="6" customWidth="1"/>
+    <col min="17" max="17" width="20.83203125" style="7" customWidth="1"/>
+    <col min="18" max="18" width="20.83203125" style="6" customWidth="1"/>
+    <col min="19" max="19" width="20.83203125" style="7" customWidth="1"/>
+    <col min="20" max="20" width="20.83203125" style="6" customWidth="1"/>
+    <col min="21" max="21" width="20.83203125" style="7" customWidth="1"/>
+    <col min="22" max="22" width="20.83203125" style="6" customWidth="1"/>
+    <col min="23" max="23" width="20.83203125" style="7" customWidth="1"/>
+    <col min="24" max="24" width="20.83203125" style="6" customWidth="1"/>
+    <col min="25" max="25" width="20.83203125" style="7" customWidth="1"/>
+    <col min="26" max="26" width="20.6640625" style="6" customWidth="1"/>
+    <col min="27" max="27" width="20.6640625" style="7" customWidth="1"/>
+    <col min="28" max="28" width="20.6640625" style="6" customWidth="1"/>
+    <col min="29" max="29" width="20.6640625" style="7" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:29" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:29" s="1" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
         <v>299</v>
       </c>
@@ -1845,7 +1845,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="3" spans="1:29" ht="60" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:29" ht="65" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="5" t="s">
         <v>3</v>
       </c>
@@ -1880,7 +1880,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="4" spans="1:29" ht="60" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:29" ht="74" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="5" t="s">
         <v>4</v>
       </c>
@@ -1909,7 +1909,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="5" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:29" ht="16" x14ac:dyDescent="0.2">
       <c r="A5" s="5" t="s">
         <v>5</v>
       </c>
@@ -1932,7 +1932,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="6" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:29" ht="32" x14ac:dyDescent="0.2">
       <c r="A6" s="5" t="s">
         <v>6</v>
       </c>
@@ -1961,7 +1961,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="7" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:29" ht="16" x14ac:dyDescent="0.2">
       <c r="A7" s="5" t="s">
         <v>7</v>
       </c>
@@ -1972,7 +1972,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:29" ht="32" x14ac:dyDescent="0.2">
       <c r="A8" s="5" t="s">
         <v>8</v>
       </c>
@@ -2001,7 +2001,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="9" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:29" ht="16" x14ac:dyDescent="0.2">
       <c r="A9" s="5" t="s">
         <v>9</v>
       </c>
@@ -2018,7 +2018,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="10" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:29" ht="16" x14ac:dyDescent="0.2">
       <c r="A10" s="5" t="s">
         <v>10</v>
       </c>
@@ -2047,7 +2047,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="11" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:29" ht="16" x14ac:dyDescent="0.2">
       <c r="A11" s="9" t="s">
         <v>11</v>
       </c>
@@ -2070,7 +2070,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="12" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:29" ht="16" x14ac:dyDescent="0.2">
       <c r="A12" s="5" t="s">
         <v>12</v>
       </c>
@@ -2087,7 +2087,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="13" spans="1:29" ht="60" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:29" ht="64" x14ac:dyDescent="0.2">
       <c r="A13" s="9" t="s">
         <v>13</v>
       </c>
@@ -2113,7 +2113,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="14" spans="1:29" ht="195" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:29" ht="167" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="9" t="s">
         <v>300</v>
       </c>
@@ -2154,7 +2154,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="15" spans="1:29" ht="45" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:29" ht="48" x14ac:dyDescent="0.2">
       <c r="A15" s="5" t="s">
         <v>14</v>
       </c>
@@ -2180,7 +2180,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="16" spans="1:29" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:29" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="5" t="s">
         <v>15</v>
       </c>
@@ -2203,7 +2203,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="17" spans="1:27" ht="45" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:27" ht="48" x14ac:dyDescent="0.2">
       <c r="A17" s="5" t="s">
         <v>16</v>
       </c>
@@ -2232,7 +2232,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="18" spans="1:27" ht="45" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:27" ht="32" x14ac:dyDescent="0.2">
       <c r="A18" s="5" t="s">
         <v>17</v>
       </c>
@@ -2252,7 +2252,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="19" spans="1:27" ht="30" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:27" ht="16" x14ac:dyDescent="0.2">
       <c r="A19" s="5" t="s">
         <v>18</v>
       </c>
@@ -2275,7 +2275,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="20" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:27" ht="16" x14ac:dyDescent="0.2">
       <c r="A20" s="5" t="s">
         <v>19</v>
       </c>
@@ -2292,7 +2292,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="21" spans="1:27" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:27" ht="380" x14ac:dyDescent="0.2">
       <c r="A21" s="9" t="s">
         <v>20</v>
       </c>
@@ -2318,7 +2318,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="22" spans="1:27" ht="30" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:27" ht="32" x14ac:dyDescent="0.2">
       <c r="A22" s="5" t="s">
         <v>21</v>
       </c>
@@ -2359,7 +2359,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="23" spans="1:27" ht="30" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:27" ht="16" x14ac:dyDescent="0.2">
       <c r="A23" s="5" t="s">
         <v>22</v>
       </c>
@@ -2388,7 +2388,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="24" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:27" ht="16" x14ac:dyDescent="0.2">
       <c r="A24" s="5" t="s">
         <v>23</v>
       </c>
@@ -2405,7 +2405,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="25" spans="1:27" ht="60" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:27" ht="48" x14ac:dyDescent="0.2">
       <c r="A25" s="9" t="s">
         <v>24</v>
       </c>
@@ -2443,7 +2443,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="26" spans="1:27" ht="30" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:27" ht="32" x14ac:dyDescent="0.2">
       <c r="A26" s="9" t="s">
         <v>25</v>
       </c>
@@ -2472,7 +2472,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="27" spans="1:27" ht="45" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:27" ht="48" x14ac:dyDescent="0.2">
       <c r="A27" s="5" t="s">
         <v>26</v>
       </c>
@@ -2516,7 +2516,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="28" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:27" ht="16" x14ac:dyDescent="0.2">
       <c r="A28" s="9" t="s">
         <v>27</v>
       </c>
@@ -2539,7 +2539,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="29" spans="1:27" ht="45" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:27" ht="48" x14ac:dyDescent="0.2">
       <c r="A29" s="5" t="s">
         <v>28</v>
       </c>
@@ -2562,7 +2562,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="30" spans="1:27" ht="45" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:27" ht="48" x14ac:dyDescent="0.2">
       <c r="A30" s="10" t="s">
         <v>28</v>
       </c>
@@ -2573,7 +2573,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:27" ht="16" x14ac:dyDescent="0.2">
       <c r="A31" s="5" t="s">
         <v>29</v>
       </c>
@@ -2602,7 +2602,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="32" spans="1:27" ht="30" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:27" ht="32" x14ac:dyDescent="0.2">
       <c r="A32" s="5" t="s">
         <v>30</v>
       </c>
@@ -2631,7 +2631,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="33" spans="1:27" ht="30" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:27" ht="16" x14ac:dyDescent="0.2">
       <c r="A33" s="9" t="s">
         <v>31</v>
       </c>
@@ -2666,7 +2666,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="34" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:27" ht="16" x14ac:dyDescent="0.2">
       <c r="A34" s="5" t="s">
         <v>5</v>
       </c>
@@ -2689,7 +2689,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="35" spans="1:27" ht="60" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:27" ht="48" x14ac:dyDescent="0.2">
       <c r="A35" s="9" t="s">
         <v>32</v>
       </c>
@@ -2724,7 +2724,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="36" spans="1:27" ht="135" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:27" ht="112" x14ac:dyDescent="0.2">
       <c r="A36" s="9" t="s">
         <v>33</v>
       </c>
@@ -2765,7 +2765,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="37" spans="1:27" ht="60" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:27" ht="64" x14ac:dyDescent="0.2">
       <c r="A37" s="9" t="s">
         <v>34</v>
       </c>
@@ -2803,7 +2803,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="38" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:27" ht="16" x14ac:dyDescent="0.2">
       <c r="A38" s="5" t="s">
         <v>35</v>
       </c>
@@ -2826,7 +2826,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="39" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:27" ht="16" x14ac:dyDescent="0.2">
       <c r="A39" s="5" t="s">
         <v>36</v>
       </c>
@@ -2849,7 +2849,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="40" spans="1:27" ht="210" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:27" ht="192" x14ac:dyDescent="0.2">
       <c r="A40" s="9" t="s">
         <v>37</v>
       </c>
@@ -2902,7 +2902,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="41" spans="1:27" ht="30" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:27" ht="32" x14ac:dyDescent="0.2">
       <c r="A41" s="9" t="s">
         <v>38</v>
       </c>
@@ -2937,7 +2937,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="42" spans="1:27" ht="45" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:27" ht="48" x14ac:dyDescent="0.2">
       <c r="A42" s="9" t="s">
         <v>39</v>
       </c>
@@ -2954,7 +2954,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="43" spans="1:27" ht="30" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:27" ht="32" x14ac:dyDescent="0.2">
       <c r="A43" s="5" t="s">
         <v>40</v>
       </c>
@@ -2980,7 +2980,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="44" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:27" ht="16" x14ac:dyDescent="0.2">
       <c r="A44" s="5" t="s">
         <v>41</v>
       </c>
@@ -3003,7 +3003,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="45" spans="1:27" ht="30" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:27" ht="32" x14ac:dyDescent="0.2">
       <c r="A45" s="5" t="s">
         <v>30</v>
       </c>
@@ -3032,7 +3032,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="46" spans="1:27" ht="30" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:27" ht="32" x14ac:dyDescent="0.2">
       <c r="A46" s="5" t="s">
         <v>42</v>
       </c>
@@ -3067,7 +3067,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="47" spans="1:27" ht="30" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:27" ht="16" x14ac:dyDescent="0.2">
       <c r="A47" s="9" t="s">
         <v>43</v>
       </c>
@@ -3102,7 +3102,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="48" spans="1:27" ht="45" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:27" ht="32" x14ac:dyDescent="0.2">
       <c r="A48" s="5" t="s">
         <v>44</v>
       </c>
@@ -3143,7 +3143,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="49" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:27" ht="16" x14ac:dyDescent="0.2">
       <c r="A49" s="5" t="s">
         <v>45</v>
       </c>
@@ -3172,7 +3172,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="50" spans="1:27" ht="30" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:27" ht="32" x14ac:dyDescent="0.2">
       <c r="A50" s="5" t="s">
         <v>46</v>
       </c>
@@ -3207,7 +3207,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="51" spans="1:27" ht="45" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:27" ht="32" x14ac:dyDescent="0.2">
       <c r="A51" s="9" t="s">
         <v>47</v>
       </c>
@@ -3242,7 +3242,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="52" spans="1:27" ht="180" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:27" ht="160" x14ac:dyDescent="0.2">
       <c r="A52" s="9" t="s">
         <v>48</v>
       </c>
@@ -3277,7 +3277,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="53" spans="1:27" ht="45" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:27" ht="48" x14ac:dyDescent="0.2">
       <c r="A53" s="5" t="s">
         <v>49</v>
       </c>
@@ -3300,7 +3300,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="54" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:27" ht="16" x14ac:dyDescent="0.2">
       <c r="A54" s="9" t="s">
         <v>50</v>
       </c>
@@ -3317,7 +3317,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="55" spans="1:27" ht="30" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:27" ht="32" x14ac:dyDescent="0.2">
       <c r="A55" s="5" t="s">
         <v>51</v>
       </c>
@@ -3352,7 +3352,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="56" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:27" ht="16" x14ac:dyDescent="0.2">
       <c r="A56" s="5" t="s">
         <v>52</v>
       </c>
@@ -3375,7 +3375,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="57" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:27" ht="16" x14ac:dyDescent="0.2">
       <c r="A57" s="5" t="s">
         <v>53</v>
       </c>
@@ -3386,7 +3386,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="58" spans="1:27" ht="30" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:27" ht="32" x14ac:dyDescent="0.2">
       <c r="A58" s="5" t="s">
         <v>54</v>
       </c>
@@ -3421,7 +3421,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="59" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:27" ht="16" x14ac:dyDescent="0.2">
       <c r="A59" s="5" t="s">
         <v>55</v>
       </c>
@@ -3444,7 +3444,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="60" spans="1:27" ht="30" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:27" ht="16" x14ac:dyDescent="0.2">
       <c r="A60" s="5" t="s">
         <v>56</v>
       </c>
@@ -3473,7 +3473,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="61" spans="1:27" ht="30" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:27" ht="32" x14ac:dyDescent="0.2">
       <c r="A61" s="9" t="s">
         <v>57</v>
       </c>
@@ -3508,7 +3508,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="62" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:27" ht="16" x14ac:dyDescent="0.2">
       <c r="A62" s="5" t="s">
         <v>52</v>
       </c>
@@ -3531,7 +3531,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="63" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:27" ht="16" x14ac:dyDescent="0.2">
       <c r="A63" s="5" t="s">
         <v>58</v>
       </c>
@@ -3548,7 +3548,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="64" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:27" ht="16" x14ac:dyDescent="0.2">
       <c r="A64" s="5" t="s">
         <v>59</v>
       </c>
@@ -3565,7 +3565,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="65" spans="1:27" ht="45" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:27" ht="32" x14ac:dyDescent="0.2">
       <c r="A65" s="5" t="s">
         <v>60</v>
       </c>
@@ -3597,7 +3597,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="66" spans="1:27" ht="30" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:27" ht="32" x14ac:dyDescent="0.2">
       <c r="A66" s="9" t="s">
         <v>61</v>
       </c>
@@ -3626,7 +3626,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="67" spans="1:27" ht="30" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:27" ht="32" x14ac:dyDescent="0.2">
       <c r="A67" s="5" t="s">
         <v>62</v>
       </c>
@@ -3658,7 +3658,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="68" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:27" ht="16" x14ac:dyDescent="0.2">
       <c r="A68" s="5" t="s">
         <v>63</v>
       </c>
@@ -3681,7 +3681,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="69" spans="1:27" ht="30" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:27" ht="32" x14ac:dyDescent="0.2">
       <c r="A69" s="5" t="s">
         <v>64</v>
       </c>
@@ -3710,7 +3710,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="70" spans="1:27" ht="45" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:27" ht="48" x14ac:dyDescent="0.2">
       <c r="A70" s="5" t="s">
         <v>65</v>
       </c>
@@ -3751,7 +3751,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="71" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:27" ht="16" x14ac:dyDescent="0.2">
       <c r="A71" s="5" t="s">
         <v>66</v>
       </c>
@@ -3774,7 +3774,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="72" spans="1:27" ht="30" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:27" ht="32" x14ac:dyDescent="0.2">
       <c r="A72" s="9" t="s">
         <v>67</v>
       </c>
@@ -3809,7 +3809,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="73" spans="1:27" ht="30" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:27" ht="32" x14ac:dyDescent="0.2">
       <c r="A73" s="5" t="s">
         <v>68</v>
       </c>
@@ -3844,7 +3844,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="74" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:27" ht="16" x14ac:dyDescent="0.2">
       <c r="A74" s="5" t="s">
         <v>29</v>
       </c>
@@ -3873,7 +3873,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="75" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:27" ht="16" x14ac:dyDescent="0.2">
       <c r="A75" s="5" t="s">
         <v>69</v>
       </c>
@@ -3896,7 +3896,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="76" spans="1:27" ht="30" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:27" ht="32" x14ac:dyDescent="0.2">
       <c r="A76" s="9" t="s">
         <v>64</v>
       </c>
@@ -3925,7 +3925,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="77" spans="1:27" ht="30" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:27" ht="16" x14ac:dyDescent="0.2">
       <c r="A77" s="5" t="s">
         <v>70</v>
       </c>
@@ -3954,7 +3954,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="78" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:27" ht="16" x14ac:dyDescent="0.2">
       <c r="A78" s="5" t="s">
         <v>71</v>
       </c>
@@ -3977,7 +3977,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="79" spans="1:27" ht="45" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:27" ht="32" x14ac:dyDescent="0.2">
       <c r="A79" s="5" t="s">
         <v>72</v>
       </c>
@@ -4018,7 +4018,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="80" spans="1:27" ht="30" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:27" ht="32" x14ac:dyDescent="0.2">
       <c r="A80" s="9" t="s">
         <v>73</v>
       </c>
@@ -4047,7 +4047,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="81" spans="1:27" ht="45" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:27" ht="32" x14ac:dyDescent="0.2">
       <c r="A81" s="5" t="s">
         <v>74</v>
       </c>
@@ -4088,7 +4088,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="82" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:27" ht="16" x14ac:dyDescent="0.2">
       <c r="A82" s="5" t="s">
         <v>75</v>
       </c>
@@ -4111,7 +4111,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="83" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:27" ht="16" x14ac:dyDescent="0.2">
       <c r="A83" s="5" t="s">
         <v>76</v>
       </c>
@@ -4140,7 +4140,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="84" spans="1:27" ht="30" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:27" ht="32" x14ac:dyDescent="0.2">
       <c r="A84" s="5" t="s">
         <v>73</v>
       </c>
@@ -4169,7 +4169,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="85" spans="1:27" ht="30" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:27" ht="32" x14ac:dyDescent="0.2">
       <c r="A85" s="5" t="s">
         <v>77</v>
       </c>
@@ -4204,7 +4204,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="86" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:27" ht="16" x14ac:dyDescent="0.2">
       <c r="A86" s="5" t="s">
         <v>78</v>
       </c>
@@ -4227,7 +4227,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="87" spans="1:27" ht="45" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:27" ht="32" x14ac:dyDescent="0.2">
       <c r="A87" s="5" t="s">
         <v>79</v>
       </c>
@@ -4256,7 +4256,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="88" spans="1:27" ht="30" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:27" ht="32" x14ac:dyDescent="0.2">
       <c r="A88" s="5" t="s">
         <v>80</v>
       </c>
@@ -4273,7 +4273,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="89" spans="1:27" ht="45" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:27" ht="32" x14ac:dyDescent="0.2">
       <c r="A89" s="9" t="s">
         <v>81</v>
       </c>
@@ -4299,7 +4299,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="90" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:27" ht="16" x14ac:dyDescent="0.2">
       <c r="A90" s="5" t="s">
         <v>82</v>
       </c>
@@ -4322,7 +4322,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="91" spans="1:27" ht="45" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:27" ht="48" x14ac:dyDescent="0.2">
       <c r="A91" s="5" t="s">
         <v>83</v>
       </c>
@@ -4357,7 +4357,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="92" spans="1:27" ht="30" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:27" ht="32" x14ac:dyDescent="0.2">
       <c r="A92" s="5" t="s">
         <v>84</v>
       </c>
@@ -4386,7 +4386,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="93" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:27" ht="16" x14ac:dyDescent="0.2">
       <c r="A93" s="9" t="s">
         <v>85</v>
       </c>
@@ -4403,7 +4403,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="94" spans="1:27" ht="45" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:27" ht="32" x14ac:dyDescent="0.2">
       <c r="A94" s="5" t="s">
         <v>86</v>
       </c>
@@ -4432,7 +4432,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="95" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:27" ht="16" x14ac:dyDescent="0.2">
       <c r="A95" s="5" t="s">
         <v>35</v>
       </c>
@@ -4455,7 +4455,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="96" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:27" ht="16" x14ac:dyDescent="0.2">
       <c r="A96" s="5" t="s">
         <v>87</v>
       </c>
@@ -4472,7 +4472,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="97" spans="1:27" ht="30" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:27" ht="32" x14ac:dyDescent="0.2">
       <c r="A97" s="9" t="s">
         <v>88</v>
       </c>
@@ -4501,7 +4501,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="98" spans="1:27" ht="45" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:27" ht="32" x14ac:dyDescent="0.2">
       <c r="A98" s="5" t="s">
         <v>89</v>
       </c>
@@ -4536,7 +4536,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="99" spans="1:27" ht="45" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:27" ht="32" x14ac:dyDescent="0.2">
       <c r="A99" s="5" t="s">
         <v>90</v>
       </c>
@@ -4559,7 +4559,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="100" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:27" ht="16" x14ac:dyDescent="0.2">
       <c r="A100" s="5" t="s">
         <v>91</v>
       </c>
@@ -4582,7 +4582,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="101" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:27" ht="16" x14ac:dyDescent="0.2">
       <c r="A101" s="9" t="s">
         <v>92</v>
       </c>
@@ -4599,7 +4599,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="102" spans="1:27" ht="45" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:27" ht="32" x14ac:dyDescent="0.2">
       <c r="A102" s="5" t="s">
         <v>93</v>
       </c>
@@ -4634,7 +4634,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="103" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:27" ht="16" x14ac:dyDescent="0.2">
       <c r="A103" s="5" t="s">
         <v>94</v>
       </c>
@@ -4651,7 +4651,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="104" spans="1:27" ht="135" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:27" ht="128" x14ac:dyDescent="0.2">
       <c r="A104" s="5" t="s">
         <v>95</v>
       </c>
@@ -4686,7 +4686,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="105" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:27" ht="16" x14ac:dyDescent="0.2">
       <c r="A105" s="5" t="s">
         <v>29</v>
       </c>
@@ -4715,7 +4715,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="106" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:27" ht="16" x14ac:dyDescent="0.2">
       <c r="A106" s="5" t="s">
         <v>96</v>
       </c>
@@ -4732,7 +4732,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="107" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:27" ht="16" x14ac:dyDescent="0.2">
       <c r="A107" s="5" t="s">
         <v>85</v>
       </c>
@@ -4749,7 +4749,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="108" spans="1:27" ht="30" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:27" ht="16" x14ac:dyDescent="0.2">
       <c r="A108" s="5" t="s">
         <v>97</v>
       </c>
@@ -4778,7 +4778,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="109" spans="1:27" ht="30" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:27" ht="32" x14ac:dyDescent="0.2">
       <c r="A109" s="5" t="s">
         <v>88</v>
       </c>
@@ -4807,7 +4807,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="110" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:27" ht="16" x14ac:dyDescent="0.2">
       <c r="A110" s="5" t="s">
         <v>98</v>
       </c>
@@ -4824,7 +4824,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="111" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:27" ht="16" x14ac:dyDescent="0.2">
       <c r="A111" s="5" t="s">
         <v>99</v>
       </c>
@@ -4853,7 +4853,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="112" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:27" ht="16" x14ac:dyDescent="0.2">
       <c r="A112" s="5" t="s">
         <v>100</v>
       </c>
@@ -4882,7 +4882,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="113" spans="1:27" ht="30" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:27" ht="32" x14ac:dyDescent="0.2">
       <c r="A113" s="5" t="s">
         <v>101</v>
       </c>
@@ -4908,7 +4908,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="114" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:27" ht="16" x14ac:dyDescent="0.2">
       <c r="A114" s="9" t="s">
         <v>102</v>
       </c>
@@ -4931,7 +4931,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="115" spans="1:27" ht="30" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:27" ht="32" x14ac:dyDescent="0.2">
       <c r="A115" s="5" t="s">
         <v>103</v>
       </c>
@@ -4960,7 +4960,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="116" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:27" ht="16" x14ac:dyDescent="0.2">
       <c r="A116" s="5" t="s">
         <v>85</v>
       </c>
@@ -4977,7 +4977,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="117" spans="1:27" ht="60" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:27" ht="48" x14ac:dyDescent="0.2">
       <c r="A117" s="5" t="s">
         <v>104</v>
       </c>
@@ -5018,7 +5018,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="118" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:27" ht="16" x14ac:dyDescent="0.2">
       <c r="A118" s="5" t="s">
         <v>105</v>
       </c>
@@ -5041,7 +5041,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="119" spans="1:27" ht="30" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:27" ht="32" x14ac:dyDescent="0.2">
       <c r="A119" s="5" t="s">
         <v>88</v>
       </c>
@@ -5070,7 +5070,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="120" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:27" ht="16" x14ac:dyDescent="0.2">
       <c r="A120" s="5" t="s">
         <v>106</v>
       </c>
@@ -5099,7 +5099,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="121" spans="1:27" ht="30" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:27" ht="32" x14ac:dyDescent="0.2">
       <c r="A121" s="5" t="s">
         <v>107</v>
       </c>
@@ -5134,7 +5134,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="122" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:27" ht="16" x14ac:dyDescent="0.2">
       <c r="A122" s="9" t="s">
         <v>108</v>
       </c>
@@ -5157,7 +5157,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="123" spans="1:27" ht="105" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:27" ht="96" x14ac:dyDescent="0.2">
       <c r="A123" s="5" t="s">
         <v>109</v>
       </c>
@@ -5186,7 +5186,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="124" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:27" ht="16" x14ac:dyDescent="0.2">
       <c r="A124" s="5" t="s">
         <v>110</v>
       </c>
@@ -5209,7 +5209,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="125" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:27" ht="16" x14ac:dyDescent="0.2">
       <c r="A125" s="9" t="s">
         <v>111</v>
       </c>
@@ -5238,7 +5238,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="126" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:27" ht="16" x14ac:dyDescent="0.2">
       <c r="A126" s="5" t="s">
         <v>59</v>
       </c>
@@ -5255,7 +5255,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="127" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:27" ht="16" x14ac:dyDescent="0.2">
       <c r="A127" s="5" t="s">
         <v>85</v>
       </c>
@@ -5272,7 +5272,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="128" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:27" ht="16" x14ac:dyDescent="0.2">
       <c r="A128" s="5" t="s">
         <v>112</v>
       </c>
@@ -5289,7 +5289,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="129" spans="1:27" ht="30" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:27" ht="32" x14ac:dyDescent="0.2">
       <c r="A129" s="5" t="s">
         <v>113</v>
       </c>
@@ -5336,7 +5336,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="130" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:27" ht="16" x14ac:dyDescent="0.2">
       <c r="A130" s="5" t="s">
         <v>114</v>
       </c>
@@ -5353,7 +5353,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="131" spans="1:27" ht="30" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:27" ht="32" x14ac:dyDescent="0.2">
       <c r="A131" s="9" t="s">
         <v>115</v>
       </c>
@@ -5382,7 +5382,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="132" spans="1:27" ht="30" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:27" ht="16" x14ac:dyDescent="0.2">
       <c r="A132" s="5" t="s">
         <v>116</v>
       </c>
@@ -5417,7 +5417,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="133" spans="1:27" ht="30" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:27" ht="32" x14ac:dyDescent="0.2">
       <c r="A133" s="5" t="s">
         <v>117</v>
       </c>
@@ -5446,7 +5446,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="134" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:27" ht="16" x14ac:dyDescent="0.2">
       <c r="A134" s="5" t="s">
         <v>118</v>
       </c>
@@ -5463,7 +5463,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="135" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:27" ht="16" x14ac:dyDescent="0.2">
       <c r="A135" s="5" t="s">
         <v>119</v>
       </c>
@@ -5486,7 +5486,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="136" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:27" ht="16" x14ac:dyDescent="0.2">
       <c r="A136" s="5" t="s">
         <v>91</v>
       </c>
@@ -5509,7 +5509,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="137" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:27" ht="16" x14ac:dyDescent="0.2">
       <c r="A137" s="5" t="s">
         <v>35</v>
       </c>
@@ -5532,7 +5532,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="138" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:27" ht="16" x14ac:dyDescent="0.2">
       <c r="A138" s="5" t="s">
         <v>87</v>
       </c>
@@ -5549,7 +5549,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="139" spans="1:27" ht="30" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:27" ht="32" x14ac:dyDescent="0.2">
       <c r="A139" s="5" t="s">
         <v>120</v>
       </c>
@@ -5578,7 +5578,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="140" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:27" ht="16" x14ac:dyDescent="0.2">
       <c r="A140" s="5" t="s">
         <v>85</v>
       </c>
@@ -5595,7 +5595,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="141" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:27" ht="16" x14ac:dyDescent="0.2">
       <c r="A141" s="5" t="s">
         <v>121</v>
       </c>
@@ -5618,7 +5618,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="142" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:27" ht="16" x14ac:dyDescent="0.2">
       <c r="A142" s="5" t="s">
         <v>122</v>
       </c>
@@ -5641,7 +5641,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="143" spans="1:27" ht="30" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:27" ht="32" x14ac:dyDescent="0.2">
       <c r="A143" s="5" t="s">
         <v>123</v>
       </c>
@@ -5670,7 +5670,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="144" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:27" ht="16" x14ac:dyDescent="0.2">
       <c r="A144" s="5" t="s">
         <v>100</v>
       </c>
@@ -5699,7 +5699,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="145" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:27" ht="16" x14ac:dyDescent="0.2">
       <c r="A145" s="5" t="s">
         <v>124</v>
       </c>
@@ -5716,7 +5716,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="146" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:27" ht="16" x14ac:dyDescent="0.2">
       <c r="A146" s="5" t="s">
         <v>125</v>
       </c>
@@ -5739,7 +5739,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="147" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:27" ht="16" x14ac:dyDescent="0.2">
       <c r="A147" s="5" t="s">
         <v>35</v>
       </c>
@@ -5762,7 +5762,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="148" spans="1:27" ht="30" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:27" ht="32" x14ac:dyDescent="0.2">
       <c r="A148" s="5" t="s">
         <v>126</v>
       </c>
@@ -5791,7 +5791,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="149" spans="1:27" ht="30" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:27" ht="16" x14ac:dyDescent="0.2">
       <c r="A149" s="5" t="s">
         <v>127</v>
       </c>
@@ -5814,7 +5814,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="150" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:27" ht="16" x14ac:dyDescent="0.2">
       <c r="A150" s="9" t="s">
         <v>75</v>
       </c>
@@ -5837,7 +5837,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="151" spans="1:27" ht="90" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:27" ht="80" x14ac:dyDescent="0.2">
       <c r="A151" s="5" t="s">
         <v>128</v>
       </c>
@@ -5872,7 +5872,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="152" spans="1:27" ht="30" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:27" ht="32" x14ac:dyDescent="0.2">
       <c r="A152" s="5" t="s">
         <v>129</v>
       </c>
@@ -5901,7 +5901,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="153" spans="1:27" ht="45" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:27" ht="48" x14ac:dyDescent="0.2">
       <c r="A153" s="5" t="s">
         <v>130</v>
       </c>
@@ -5942,7 +5942,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="154" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:27" ht="16" x14ac:dyDescent="0.2">
       <c r="A154" s="5" t="s">
         <v>131</v>
       </c>
@@ -5959,7 +5959,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="155" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:27" ht="16" x14ac:dyDescent="0.2">
       <c r="A155" s="9" t="s">
         <v>132</v>
       </c>
@@ -5988,7 +5988,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="156" spans="1:27" ht="30" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:27" ht="32" x14ac:dyDescent="0.2">
       <c r="A156" s="5" t="s">
         <v>133</v>
       </c>
@@ -6029,7 +6029,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="157" spans="1:27" ht="30" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:27" ht="32" x14ac:dyDescent="0.2">
       <c r="A157" s="9" t="s">
         <v>134</v>
       </c>
@@ -6058,7 +6058,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="158" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:27" ht="16" x14ac:dyDescent="0.2">
       <c r="A158" s="5" t="s">
         <v>35</v>
       </c>
@@ -6081,7 +6081,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="159" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:27" ht="16" x14ac:dyDescent="0.2">
       <c r="A159" s="5" t="s">
         <v>135</v>
       </c>
@@ -6098,7 +6098,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="160" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:27" ht="16" x14ac:dyDescent="0.2">
       <c r="A160" s="5" t="s">
         <v>87</v>
       </c>
@@ -6115,7 +6115,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="161" spans="1:27" ht="45" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:27" ht="32" x14ac:dyDescent="0.2">
       <c r="A161" s="5" t="s">
         <v>136</v>
       </c>
@@ -6156,7 +6156,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="162" spans="1:27" ht="30" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:27" ht="32" x14ac:dyDescent="0.2">
       <c r="A162" s="5" t="s">
         <v>137</v>
       </c>
@@ -6191,7 +6191,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="163" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:27" ht="16" x14ac:dyDescent="0.2">
       <c r="A163" s="5" t="s">
         <v>29</v>
       </c>
@@ -6220,7 +6220,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="164" spans="1:27" ht="60" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:27" ht="64" x14ac:dyDescent="0.2">
       <c r="A164" s="5" t="s">
         <v>138</v>
       </c>
@@ -6243,7 +6243,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="165" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:27" ht="16" x14ac:dyDescent="0.2">
       <c r="A165" s="5" t="s">
         <v>139</v>
       </c>
@@ -6266,7 +6266,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="166" spans="1:27" ht="30" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:27" ht="32" x14ac:dyDescent="0.2">
       <c r="A166" s="5" t="s">
         <v>8</v>
       </c>
@@ -6295,7 +6295,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="167" spans="1:27" ht="30" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:27" ht="32" x14ac:dyDescent="0.2">
       <c r="A167" s="5" t="s">
         <v>140</v>
       </c>
@@ -6324,7 +6324,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="168" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:27" ht="16" x14ac:dyDescent="0.2">
       <c r="A168" s="5" t="s">
         <v>141</v>
       </c>
@@ -6341,7 +6341,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="169" spans="1:27" ht="30" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:27" ht="16" x14ac:dyDescent="0.2">
       <c r="A169" s="5" t="s">
         <v>43</v>
       </c>
@@ -6376,7 +6376,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="170" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:27" ht="16" x14ac:dyDescent="0.2">
       <c r="A170" s="5" t="s">
         <v>142</v>
       </c>
@@ -6399,7 +6399,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="171" spans="1:27" ht="45" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:27" ht="32" x14ac:dyDescent="0.2">
       <c r="A171" s="5" t="s">
         <v>72</v>
       </c>
@@ -6440,7 +6440,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="172" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:27" ht="16" x14ac:dyDescent="0.2">
       <c r="A172" s="5" t="s">
         <v>143</v>
       </c>
@@ -6457,7 +6457,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="173" spans="1:27" ht="30" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:27" ht="32" x14ac:dyDescent="0.2">
       <c r="A173" s="5" t="s">
         <v>30</v>
       </c>
@@ -6486,7 +6486,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="174" spans="1:27" ht="30" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:27" ht="32" x14ac:dyDescent="0.2">
       <c r="A174" s="5" t="s">
         <v>144</v>
       </c>
@@ -6515,7 +6515,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="175" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:27" ht="16" x14ac:dyDescent="0.2">
       <c r="A175" s="5" t="s">
         <v>29</v>
       </c>
@@ -6544,7 +6544,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="176" spans="1:27" ht="30" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:27" ht="32" x14ac:dyDescent="0.2">
       <c r="A176" s="5" t="s">
         <v>30</v>
       </c>
@@ -6573,7 +6573,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="177" spans="1:27" ht="30" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:27" ht="16" x14ac:dyDescent="0.2">
       <c r="A177" s="5" t="s">
         <v>145</v>
       </c>
@@ -6608,7 +6608,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="178" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:27" ht="16" x14ac:dyDescent="0.2">
       <c r="A178" s="5" t="s">
         <v>146</v>
       </c>
@@ -6625,7 +6625,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="179" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:27" ht="16" x14ac:dyDescent="0.2">
       <c r="A179" s="5" t="s">
         <v>147</v>
       </c>
@@ -6648,7 +6648,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="180" spans="1:27" ht="30" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:27" ht="32" x14ac:dyDescent="0.2">
       <c r="A180" s="5" t="s">
         <v>148</v>
       </c>
@@ -6671,7 +6671,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="181" spans="1:27" ht="45" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:27" ht="48" x14ac:dyDescent="0.2">
       <c r="A181" s="5" t="s">
         <v>149</v>
       </c>
@@ -6700,7 +6700,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="182" spans="1:27" ht="135" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:27" ht="128" x14ac:dyDescent="0.2">
       <c r="A182" s="5" t="s">
         <v>150</v>
       </c>
@@ -6735,7 +6735,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="183" spans="1:27" ht="45" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:27" ht="48" x14ac:dyDescent="0.2">
       <c r="A183" s="5" t="s">
         <v>151</v>
       </c>
@@ -6776,7 +6776,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="184" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:27" ht="16" x14ac:dyDescent="0.2">
       <c r="A184" s="5" t="s">
         <v>36</v>
       </c>
@@ -6799,7 +6799,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="185" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:27" ht="16" x14ac:dyDescent="0.2">
       <c r="A185" s="5" t="s">
         <v>152</v>
       </c>
@@ -6816,7 +6816,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="186" spans="1:27" ht="165" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:27" ht="144" x14ac:dyDescent="0.2">
       <c r="A186" s="5" t="s">
         <v>153</v>
       </c>
@@ -6848,7 +6848,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="187" spans="1:27" ht="30" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:27" ht="32" x14ac:dyDescent="0.2">
       <c r="A187" s="5" t="s">
         <v>154</v>
       </c>
@@ -6877,7 +6877,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="188" spans="1:27" ht="30" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:27" ht="32" x14ac:dyDescent="0.2">
       <c r="A188" s="5" t="s">
         <v>155</v>
       </c>
@@ -6906,7 +6906,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="189" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:27" ht="16" x14ac:dyDescent="0.2">
       <c r="A189" s="5" t="s">
         <v>41</v>
       </c>
@@ -6929,7 +6929,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="190" spans="1:27" ht="30" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:27" ht="32" x14ac:dyDescent="0.2">
       <c r="A190" s="5" t="s">
         <v>156</v>
       </c>
@@ -6964,7 +6964,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="191" spans="1:27" ht="30" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:27" ht="32" x14ac:dyDescent="0.2">
       <c r="A191" s="5" t="s">
         <v>42</v>
       </c>
@@ -6993,7 +6993,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="192" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:27" ht="16" x14ac:dyDescent="0.2">
       <c r="A192" s="5" t="s">
         <v>157</v>
       </c>
@@ -7022,7 +7022,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="193" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:27" ht="16" x14ac:dyDescent="0.2">
       <c r="A193" s="5" t="s">
         <v>158</v>
       </c>
@@ -7057,7 +7057,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="194" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:27" ht="16" x14ac:dyDescent="0.2">
       <c r="A194" s="5" t="s">
         <v>52</v>
       </c>
@@ -7080,7 +7080,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="195" spans="1:27" ht="30" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:27" ht="32" x14ac:dyDescent="0.2">
       <c r="A195" s="5" t="s">
         <v>159</v>
       </c>
@@ -7109,7 +7109,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="196" spans="1:27" ht="45" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:27" ht="32" x14ac:dyDescent="0.2">
       <c r="A196" s="5" t="s">
         <v>160</v>
       </c>
@@ -7144,7 +7144,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="197" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:27" ht="16" x14ac:dyDescent="0.2">
       <c r="A197" s="5" t="s">
         <v>114</v>
       </c>
@@ -7161,7 +7161,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="198" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:27" ht="16" x14ac:dyDescent="0.2">
       <c r="A198" s="5" t="s">
         <v>50</v>
       </c>
@@ -7178,7 +7178,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="199" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:27" ht="16" x14ac:dyDescent="0.2">
       <c r="A199" s="5" t="s">
         <v>29</v>
       </c>
@@ -7207,7 +7207,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="200" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:27" ht="16" x14ac:dyDescent="0.2">
       <c r="A200" s="5" t="s">
         <v>35</v>
       </c>
@@ -7230,7 +7230,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="201" spans="1:27" ht="30" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:27" ht="32" x14ac:dyDescent="0.2">
       <c r="A201" s="5" t="s">
         <v>161</v>
       </c>
@@ -7265,7 +7265,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="202" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:27" ht="16" x14ac:dyDescent="0.2">
       <c r="A202" s="5" t="s">
         <v>55</v>
       </c>
@@ -7288,7 +7288,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="203" spans="1:27" ht="30" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:27" ht="16" x14ac:dyDescent="0.2">
       <c r="A203" s="5" t="s">
         <v>162</v>
       </c>
@@ -7323,7 +7323,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="204" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:27" ht="16" x14ac:dyDescent="0.2">
       <c r="A204" s="5" t="s">
         <v>29</v>
       </c>
@@ -7352,7 +7352,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="205" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:27" ht="16" x14ac:dyDescent="0.2">
       <c r="A205" s="5" t="s">
         <v>52</v>
       </c>
@@ -7375,7 +7375,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="206" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:27" ht="16" x14ac:dyDescent="0.2">
       <c r="A206" s="5" t="s">
         <v>87</v>
       </c>
@@ -7392,7 +7392,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="207" spans="1:27" ht="30" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:27" ht="32" x14ac:dyDescent="0.2">
       <c r="A207" s="5" t="s">
         <v>163</v>
       </c>
@@ -7421,7 +7421,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="208" spans="1:27" ht="30" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:27" ht="32" x14ac:dyDescent="0.2">
       <c r="A208" s="5" t="s">
         <v>164</v>
       </c>
@@ -7450,7 +7450,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="209" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:27" ht="16" x14ac:dyDescent="0.2">
       <c r="A209" s="5" t="s">
         <v>29</v>
       </c>
@@ -7479,7 +7479,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="210" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:27" ht="16" x14ac:dyDescent="0.2">
       <c r="A210" s="5" t="s">
         <v>139</v>
       </c>
@@ -7502,7 +7502,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="211" spans="1:27" ht="30" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:27" ht="32" x14ac:dyDescent="0.2">
       <c r="A211" s="5" t="s">
         <v>165</v>
       </c>
@@ -7537,7 +7537,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="212" spans="1:27" ht="30" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:27" ht="32" x14ac:dyDescent="0.2">
       <c r="A212" s="5" t="s">
         <v>165</v>
       </c>
@@ -7572,7 +7572,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="213" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:27" ht="16" x14ac:dyDescent="0.2">
       <c r="A213" s="5" t="s">
         <v>166</v>
       </c>
@@ -7589,7 +7589,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="214" spans="1:27" ht="45" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:27" ht="32" x14ac:dyDescent="0.2">
       <c r="A214" s="5" t="s">
         <v>167</v>
       </c>
@@ -7618,7 +7618,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="215" spans="1:27" ht="45" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:27" ht="48" x14ac:dyDescent="0.2">
       <c r="A215" s="5" t="s">
         <v>168</v>
       </c>
@@ -7641,7 +7641,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="216" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:27" ht="16" x14ac:dyDescent="0.2">
       <c r="A216" s="5" t="s">
         <v>36</v>
       </c>
@@ -7664,7 +7664,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="217" spans="1:27" ht="30" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:27" ht="32" x14ac:dyDescent="0.2">
       <c r="A217" s="5" t="s">
         <v>169</v>
       </c>
@@ -7699,7 +7699,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="218" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:27" ht="16" x14ac:dyDescent="0.2">
       <c r="A218" s="5" t="s">
         <v>170</v>
       </c>
@@ -7728,7 +7728,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="219" spans="1:27" ht="60" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:27" ht="64" x14ac:dyDescent="0.2">
       <c r="A219" s="5" t="s">
         <v>171</v>
       </c>
@@ -7775,7 +7775,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="220" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:27" ht="16" x14ac:dyDescent="0.2">
       <c r="A220" s="5" t="s">
         <v>172</v>
       </c>
@@ -7798,7 +7798,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="221" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:27" ht="16" x14ac:dyDescent="0.2">
       <c r="A221" s="5" t="s">
         <v>29</v>
       </c>
@@ -7827,7 +7827,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="222" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:27" ht="16" x14ac:dyDescent="0.2">
       <c r="A222" s="5" t="s">
         <v>106</v>
       </c>
@@ -7856,7 +7856,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="223" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:27" ht="16" x14ac:dyDescent="0.2">
       <c r="A223" s="5" t="s">
         <v>173</v>
       </c>
@@ -7885,7 +7885,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="224" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:27" ht="16" x14ac:dyDescent="0.2">
       <c r="A224" s="5" t="s">
         <v>174</v>
       </c>
@@ -7902,7 +7902,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="225" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:27" ht="16" x14ac:dyDescent="0.2">
       <c r="A225" s="5" t="s">
         <v>119</v>
       </c>
@@ -7922,7 +7922,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="226" spans="1:27" ht="30" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:27" ht="32" x14ac:dyDescent="0.2">
       <c r="A226" s="5" t="s">
         <v>175</v>
       </c>
@@ -7951,7 +7951,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="227" spans="1:27" ht="45" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:27" ht="32" x14ac:dyDescent="0.2">
       <c r="A227" s="5" t="s">
         <v>176</v>
       </c>
@@ -7992,7 +7992,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="228" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:27" ht="16" x14ac:dyDescent="0.2">
       <c r="A228" s="5" t="s">
         <v>177</v>
       </c>
@@ -8015,7 +8015,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="229" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:27" ht="16" x14ac:dyDescent="0.2">
       <c r="A229" s="5" t="s">
         <v>178</v>
       </c>
@@ -8038,7 +8038,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="230" spans="1:27" ht="30" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:27" ht="32" x14ac:dyDescent="0.2">
       <c r="A230" s="5" t="s">
         <v>179</v>
       </c>
@@ -8070,7 +8070,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="231" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:27" ht="16" x14ac:dyDescent="0.2">
       <c r="A231" s="5" t="s">
         <v>180</v>
       </c>
@@ -8093,7 +8093,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="232" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:27" ht="16" x14ac:dyDescent="0.2">
       <c r="A232" s="5" t="s">
         <v>36</v>
       </c>
@@ -8116,7 +8116,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="233" spans="1:27" ht="30" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:27" ht="32" x14ac:dyDescent="0.2">
       <c r="A233" s="5" t="s">
         <v>181</v>
       </c>
@@ -8139,7 +8139,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="234" spans="1:27" ht="60" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:27" ht="64" x14ac:dyDescent="0.2">
       <c r="A234" s="5" t="s">
         <v>182</v>
       </c>
@@ -8156,7 +8156,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="235" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:27" ht="16" x14ac:dyDescent="0.2">
       <c r="A235" s="5" t="s">
         <v>183</v>
       </c>
@@ -8167,7 +8167,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="236" spans="1:27" ht="45" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:27" ht="48" x14ac:dyDescent="0.2">
       <c r="A236" s="5" t="s">
         <v>184</v>
       </c>
@@ -8202,7 +8202,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="237" spans="1:27" ht="150" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:27" ht="144" x14ac:dyDescent="0.2">
       <c r="A237" s="5" t="s">
         <v>185</v>
       </c>
@@ -8249,7 +8249,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="238" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:27" ht="16" x14ac:dyDescent="0.2">
       <c r="A238" s="5" t="s">
         <v>186</v>
       </c>
@@ -8266,7 +8266,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="239" spans="1:27" ht="45" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:27" ht="32" x14ac:dyDescent="0.2">
       <c r="A239" s="5" t="s">
         <v>187</v>
       </c>
@@ -8301,7 +8301,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="240" spans="1:27" ht="30" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:27" ht="32" x14ac:dyDescent="0.2">
       <c r="A240" s="5" t="s">
         <v>30</v>
       </c>
@@ -8330,7 +8330,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="241" spans="1:27" ht="45" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:27" ht="48" x14ac:dyDescent="0.2">
       <c r="A241" s="5" t="s">
         <v>188</v>
       </c>
@@ -8371,7 +8371,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="242" spans="1:27" ht="30" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:27" ht="32" x14ac:dyDescent="0.2">
       <c r="A242" s="5" t="s">
         <v>189</v>
       </c>
@@ -8400,7 +8400,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="243" spans="1:27" ht="60" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:27" ht="48" x14ac:dyDescent="0.2">
       <c r="A243" s="5" t="s">
         <v>190</v>
       </c>
@@ -8441,7 +8441,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="244" spans="1:27" ht="30" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:27" ht="16" x14ac:dyDescent="0.2">
       <c r="A244" s="5" t="s">
         <v>191</v>
       </c>
@@ -8476,7 +8476,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="245" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:27" ht="16" x14ac:dyDescent="0.2">
       <c r="A245" s="5" t="s">
         <v>192</v>
       </c>
@@ -8493,7 +8493,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="246" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:27" ht="16" x14ac:dyDescent="0.2">
       <c r="A246" s="5" t="s">
         <v>193</v>
       </c>
@@ -8516,7 +8516,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="247" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:27" ht="16" x14ac:dyDescent="0.2">
       <c r="A247" s="5" t="s">
         <v>36</v>
       </c>
@@ -8539,7 +8539,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="248" spans="1:27" ht="30" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:27" ht="32" x14ac:dyDescent="0.2">
       <c r="A248" s="5" t="s">
         <v>194</v>
       </c>
@@ -8580,7 +8580,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="249" spans="1:27" ht="30" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:27" ht="32" x14ac:dyDescent="0.2">
       <c r="A249" s="5" t="s">
         <v>195</v>
       </c>
@@ -8621,7 +8621,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="250" spans="1:27" ht="30" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:27" ht="32" x14ac:dyDescent="0.2">
       <c r="A250" s="5" t="s">
         <v>196</v>
       </c>
@@ -8650,7 +8650,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="251" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:27" ht="16" x14ac:dyDescent="0.2">
       <c r="A251" s="5" t="s">
         <v>59</v>
       </c>
@@ -8667,7 +8667,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="252" spans="1:27" ht="30" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:27" ht="16" x14ac:dyDescent="0.2">
       <c r="A252" s="5" t="s">
         <v>197</v>
       </c>
@@ -8696,7 +8696,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="253" spans="1:27" ht="30" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:27" ht="32" x14ac:dyDescent="0.2">
       <c r="A253" s="5" t="s">
         <v>198</v>
       </c>
@@ -8725,7 +8725,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="254" spans="1:27" ht="45" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:27" ht="32" x14ac:dyDescent="0.2">
       <c r="A254" s="5" t="s">
         <v>199</v>
       </c>
@@ -8766,7 +8766,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="255" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:27" ht="16" x14ac:dyDescent="0.2">
       <c r="A255" s="5" t="s">
         <v>200</v>
       </c>
@@ -8783,7 +8783,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="256" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:27" ht="16" x14ac:dyDescent="0.2">
       <c r="A256" s="5" t="s">
         <v>200</v>
       </c>
@@ -8800,7 +8800,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="257" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:27" ht="16" x14ac:dyDescent="0.2">
       <c r="A257" s="5" t="s">
         <v>201</v>
       </c>
@@ -8823,7 +8823,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="258" spans="1:27" ht="45" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:27" ht="32" x14ac:dyDescent="0.2">
       <c r="A258" s="5" t="s">
         <v>176</v>
       </c>
@@ -8864,7 +8864,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="259" spans="1:27" ht="30" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:27" ht="16" x14ac:dyDescent="0.2">
       <c r="A259" s="5" t="s">
         <v>202</v>
       </c>
@@ -8890,7 +8890,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="260" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:27" ht="16" x14ac:dyDescent="0.2">
       <c r="A260" s="5" t="s">
         <v>55</v>
       </c>
@@ -8913,7 +8913,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="261" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:27" ht="16" x14ac:dyDescent="0.2">
       <c r="A261" s="5" t="s">
         <v>203</v>
       </c>
@@ -8936,7 +8936,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="262" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:27" ht="16" x14ac:dyDescent="0.2">
       <c r="A262" s="5" t="s">
         <v>204</v>
       </c>
@@ -8959,7 +8959,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="263" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:27" ht="16" x14ac:dyDescent="0.2">
       <c r="A263" s="5" t="s">
         <v>205</v>
       </c>
@@ -8976,7 +8976,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="264" spans="1:27" ht="30" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:27" ht="16" x14ac:dyDescent="0.2">
       <c r="A264" s="5" t="s">
         <v>206</v>
       </c>
@@ -8999,7 +8999,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="265" spans="1:27" ht="135" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:27" ht="112" x14ac:dyDescent="0.2">
       <c r="A265" s="5" t="s">
         <v>207</v>
       </c>
@@ -9034,7 +9034,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="266" spans="1:27" ht="105" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:27" ht="80" x14ac:dyDescent="0.2">
       <c r="A266" s="5" t="s">
         <v>209</v>
       </c>
@@ -9045,7 +9045,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="267" spans="1:27" ht="180" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:27" ht="160" x14ac:dyDescent="0.2">
       <c r="A267" s="5" t="s">
         <v>210</v>
       </c>
@@ -9080,7 +9080,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="268" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:27" ht="16" x14ac:dyDescent="0.2">
       <c r="A268" s="5" t="s">
         <v>211</v>
       </c>
@@ -9097,7 +9097,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="269" spans="1:27" ht="30" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:27" ht="32" x14ac:dyDescent="0.2">
       <c r="A269" s="5" t="s">
         <v>212</v>
       </c>
@@ -9120,7 +9120,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="270" spans="1:27" ht="210" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:27" ht="192" x14ac:dyDescent="0.2">
       <c r="A270" s="5" t="s">
         <v>213</v>
       </c>
@@ -9161,7 +9161,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="271" spans="1:27" ht="60" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:27" ht="48" x14ac:dyDescent="0.2">
       <c r="A271" s="5" t="s">
         <v>214</v>
       </c>
@@ -9202,7 +9202,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="272" spans="1:27" ht="300" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:27" ht="272" x14ac:dyDescent="0.2">
       <c r="A272" s="5" t="s">
         <v>215</v>
       </c>
@@ -9249,7 +9249,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="273" spans="1:29" ht="75" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:29" ht="64" x14ac:dyDescent="0.2">
       <c r="A273" s="5" t="s">
         <v>216</v>
       </c>
@@ -9272,7 +9272,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="274" spans="1:29" ht="75" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:29" ht="64" x14ac:dyDescent="0.2">
       <c r="A274" s="5" t="s">
         <v>217</v>
       </c>
@@ -9313,7 +9313,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="275" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:29" ht="32" x14ac:dyDescent="0.2">
       <c r="A275" s="5" t="s">
         <v>218</v>
       </c>
@@ -9348,7 +9348,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="276" spans="1:29" ht="135" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:29" ht="128" x14ac:dyDescent="0.2">
       <c r="A276" s="5" t="s">
         <v>219</v>
       </c>
@@ -9386,7 +9386,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="277" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:29" ht="32" x14ac:dyDescent="0.2">
       <c r="A277" s="5" t="s">
         <v>220</v>
       </c>
@@ -9415,7 +9415,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="278" spans="1:29" ht="105" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:29" ht="96" x14ac:dyDescent="0.2">
       <c r="A278" s="5" t="s">
         <v>221</v>
       </c>
@@ -9438,7 +9438,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="279" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:29" ht="32" x14ac:dyDescent="0.2">
       <c r="A279" s="5" t="s">
         <v>222</v>
       </c>
@@ -9461,7 +9461,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="280" spans="1:29" ht="150" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:29" ht="144" x14ac:dyDescent="0.2">
       <c r="A280" s="5" t="s">
         <v>223</v>
       </c>
@@ -9508,7 +9508,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="281" spans="1:29" ht="90" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:29" ht="80" x14ac:dyDescent="0.2">
       <c r="A281" s="5" t="s">
         <v>224</v>
       </c>
@@ -9537,7 +9537,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="282" spans="1:29" ht="135" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:29" ht="112" x14ac:dyDescent="0.2">
       <c r="A282" s="5" t="s">
         <v>225</v>
       </c>
@@ -9590,7 +9590,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="283" spans="1:29" ht="60" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:29" ht="48" x14ac:dyDescent="0.2">
       <c r="A283" s="5" t="s">
         <v>226</v>
       </c>
@@ -9616,7 +9616,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="284" spans="1:29" ht="195" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:29" ht="176" x14ac:dyDescent="0.2">
       <c r="A284" s="5" t="s">
         <v>227</v>
       </c>
@@ -9672,7 +9672,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="285" spans="1:29" ht="180" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:29" ht="144" x14ac:dyDescent="0.2">
       <c r="A285" s="5" t="s">
         <v>228</v>
       </c>
@@ -9725,7 +9725,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="286" spans="1:29" ht="60" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:29" ht="64" x14ac:dyDescent="0.2">
       <c r="A286" s="5" t="s">
         <v>229</v>
       </c>
@@ -9772,7 +9772,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="287" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:29" ht="16" x14ac:dyDescent="0.2">
       <c r="A287" s="5" t="s">
         <v>230</v>
       </c>
@@ -9789,7 +9789,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="288" spans="1:29" ht="210" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:29" ht="192" x14ac:dyDescent="0.2">
       <c r="A288" s="5" t="s">
         <v>231</v>
       </c>
@@ -9836,7 +9836,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="289" spans="1:29" ht="60" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:29" ht="48" x14ac:dyDescent="0.2">
       <c r="A289" s="5" t="s">
         <v>232</v>
       </c>
@@ -9883,7 +9883,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="290" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:29" ht="16" x14ac:dyDescent="0.2">
       <c r="A290" s="5" t="s">
         <v>233</v>
       </c>
@@ -9900,7 +9900,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="291" spans="1:29" ht="255" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:29" ht="240" x14ac:dyDescent="0.2">
       <c r="A291" s="5" t="s">
         <v>234</v>
       </c>
@@ -9959,7 +9959,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="292" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:29" ht="32" x14ac:dyDescent="0.2">
       <c r="A292" s="5" t="s">
         <v>235</v>
       </c>
@@ -9982,7 +9982,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="293" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:29" ht="32" x14ac:dyDescent="0.2">
       <c r="A293" s="5" t="s">
         <v>236</v>
       </c>
@@ -10011,7 +10011,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="294" spans="1:29" ht="105" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:29" ht="96" x14ac:dyDescent="0.2">
       <c r="A294" s="5" t="s">
         <v>237</v>
       </c>
@@ -10052,7 +10052,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="295" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:29" ht="16" x14ac:dyDescent="0.2">
       <c r="A295" s="5" t="s">
         <v>238</v>
       </c>
@@ -10081,7 +10081,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="296" spans="1:29" ht="180" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:29" ht="160" x14ac:dyDescent="0.2">
       <c r="A296" s="5" t="s">
         <v>239</v>
       </c>
@@ -10122,7 +10122,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="297" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:29" ht="32" x14ac:dyDescent="0.2">
       <c r="A297" s="5" t="s">
         <v>240</v>
       </c>
@@ -10157,7 +10157,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="298" spans="1:29" ht="60" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:29" ht="48" x14ac:dyDescent="0.2">
       <c r="A298" s="5" t="s">
         <v>241</v>
       </c>
@@ -10192,7 +10192,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="299" spans="1:29" ht="60" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:29" ht="48" x14ac:dyDescent="0.2">
       <c r="A299" s="5" t="s">
         <v>242</v>
       </c>
@@ -10233,7 +10233,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="300" spans="1:29" ht="45" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:29" ht="32" x14ac:dyDescent="0.2">
       <c r="A300" s="5" t="s">
         <v>243</v>
       </c>
@@ -10274,7 +10274,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="301" spans="1:29" ht="105" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:29" ht="80" x14ac:dyDescent="0.2">
       <c r="A301" s="10" t="s">
         <v>209</v>
       </c>
@@ -10291,7 +10291,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="302" spans="1:29" ht="180" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:29" ht="160" x14ac:dyDescent="0.2">
       <c r="A302" s="10" t="s">
         <v>210</v>
       </c>
@@ -10308,7 +10308,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="303" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:29" ht="16" x14ac:dyDescent="0.2">
       <c r="A303" s="10" t="s">
         <v>211</v>
       </c>
@@ -10319,7 +10319,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="304" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:29" ht="32" x14ac:dyDescent="0.2">
       <c r="A304" s="10" t="s">
         <v>212</v>
       </c>
@@ -10330,7 +10330,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="305" spans="1:3" ht="210" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:3" ht="192" x14ac:dyDescent="0.2">
       <c r="A305" s="10" t="s">
         <v>213</v>
       </c>
@@ -10341,7 +10341,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="306" spans="1:3" ht="60" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:3" ht="48" x14ac:dyDescent="0.2">
       <c r="A306" s="10" t="s">
         <v>214</v>
       </c>
@@ -10352,7 +10352,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="307" spans="1:3" ht="300" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:3" ht="272" x14ac:dyDescent="0.2">
       <c r="A307" s="10" t="s">
         <v>215</v>
       </c>
@@ -10363,7 +10363,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="308" spans="1:3" ht="75" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:3" ht="64" x14ac:dyDescent="0.2">
       <c r="A308" s="10" t="s">
         <v>216</v>
       </c>
@@ -10374,7 +10374,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="309" spans="1:3" ht="75" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:3" ht="64" x14ac:dyDescent="0.2">
       <c r="A309" s="10" t="s">
         <v>217</v>
       </c>
@@ -10385,7 +10385,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="310" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:3" ht="32" x14ac:dyDescent="0.2">
       <c r="A310" s="10" t="s">
         <v>218</v>
       </c>
@@ -10396,7 +10396,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="311" spans="1:3" ht="135" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:3" ht="128" x14ac:dyDescent="0.2">
       <c r="A311" s="10" t="s">
         <v>219</v>
       </c>
@@ -10407,7 +10407,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="312" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:3" ht="32" x14ac:dyDescent="0.2">
       <c r="A312" s="10" t="s">
         <v>220</v>
       </c>
@@ -10418,7 +10418,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="313" spans="1:3" ht="105" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:3" ht="96" x14ac:dyDescent="0.2">
       <c r="A313" s="10" t="s">
         <v>221</v>
       </c>
@@ -10429,7 +10429,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="314" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:3" ht="32" x14ac:dyDescent="0.2">
       <c r="A314" s="10" t="s">
         <v>222</v>
       </c>
@@ -10440,7 +10440,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="315" spans="1:3" ht="150" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:3" ht="144" x14ac:dyDescent="0.2">
       <c r="A315" s="10" t="s">
         <v>223</v>
       </c>
@@ -10451,7 +10451,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="316" spans="1:3" ht="90" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:3" ht="80" x14ac:dyDescent="0.2">
       <c r="A316" s="10" t="s">
         <v>224</v>
       </c>
@@ -10462,7 +10462,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="317" spans="1:3" ht="135" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:3" ht="112" x14ac:dyDescent="0.2">
       <c r="A317" s="10" t="s">
         <v>225</v>
       </c>
@@ -10473,7 +10473,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="318" spans="1:3" ht="60" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:3" ht="48" x14ac:dyDescent="0.2">
       <c r="A318" s="10" t="s">
         <v>226</v>
       </c>
@@ -10484,7 +10484,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="319" spans="1:3" ht="195" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:3" ht="176" x14ac:dyDescent="0.2">
       <c r="A319" s="10" t="s">
         <v>227</v>
       </c>
@@ -10495,7 +10495,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="320" spans="1:3" ht="180" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:3" ht="144" x14ac:dyDescent="0.2">
       <c r="A320" s="10" t="s">
         <v>228</v>
       </c>
@@ -10506,7 +10506,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="321" spans="1:27" ht="60" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:27" ht="64" x14ac:dyDescent="0.2">
       <c r="A321" s="10" t="s">
         <v>229</v>
       </c>
@@ -10517,7 +10517,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="322" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:27" ht="16" x14ac:dyDescent="0.2">
       <c r="A322" s="10" t="s">
         <v>230</v>
       </c>
@@ -10528,7 +10528,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="323" spans="1:27" ht="210" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:27" ht="192" x14ac:dyDescent="0.2">
       <c r="A323" s="10" t="s">
         <v>231</v>
       </c>
@@ -10539,7 +10539,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="324" spans="1:27" ht="60" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:27" ht="48" x14ac:dyDescent="0.2">
       <c r="A324" s="10" t="s">
         <v>232</v>
       </c>
@@ -10550,7 +10550,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="325" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:27" ht="16" x14ac:dyDescent="0.2">
       <c r="A325" s="10" t="s">
         <v>233</v>
       </c>
@@ -10561,7 +10561,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="326" spans="1:27" ht="255" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:27" ht="240" x14ac:dyDescent="0.2">
       <c r="A326" s="10" t="s">
         <v>234</v>
       </c>
@@ -10572,7 +10572,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="327" spans="1:27" ht="30" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:27" ht="32" x14ac:dyDescent="0.2">
       <c r="A327" s="10" t="s">
         <v>235</v>
       </c>
@@ -10583,7 +10583,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="328" spans="1:27" ht="30" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:27" ht="32" x14ac:dyDescent="0.2">
       <c r="A328" s="10" t="s">
         <v>236</v>
       </c>
@@ -10594,7 +10594,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="329" spans="1:27" ht="105" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:27" ht="96" x14ac:dyDescent="0.2">
       <c r="A329" s="10" t="s">
         <v>237</v>
       </c>
@@ -10605,7 +10605,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="330" spans="1:27" ht="30" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:27" ht="16" x14ac:dyDescent="0.2">
       <c r="A330" s="10" t="s">
         <v>238</v>
       </c>
@@ -10616,7 +10616,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="331" spans="1:27" ht="180" x14ac:dyDescent="0.25">
+    <row r="331" spans="1:27" ht="160" x14ac:dyDescent="0.2">
       <c r="A331" s="10" t="s">
         <v>239</v>
       </c>
@@ -10627,7 +10627,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="332" spans="1:27" ht="30" x14ac:dyDescent="0.25">
+    <row r="332" spans="1:27" ht="32" x14ac:dyDescent="0.2">
       <c r="A332" s="10" t="s">
         <v>240</v>
       </c>
@@ -10638,7 +10638,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="333" spans="1:27" ht="60" x14ac:dyDescent="0.25">
+    <row r="333" spans="1:27" ht="48" x14ac:dyDescent="0.2">
       <c r="A333" s="10" t="s">
         <v>241</v>
       </c>
@@ -10649,7 +10649,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="334" spans="1:27" ht="60" x14ac:dyDescent="0.25">
+    <row r="334" spans="1:27" ht="48" x14ac:dyDescent="0.2">
       <c r="A334" s="10" t="s">
         <v>242</v>
       </c>
@@ -10660,7 +10660,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="335" spans="1:27" ht="45" x14ac:dyDescent="0.25">
+    <row r="335" spans="1:27" ht="32" x14ac:dyDescent="0.2">
       <c r="A335" s="10" t="s">
         <v>243</v>
       </c>
@@ -10671,7 +10671,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="336" spans="1:27" ht="45" x14ac:dyDescent="0.25">
+    <row r="336" spans="1:27" ht="32" x14ac:dyDescent="0.2">
       <c r="A336" s="5" t="s">
         <v>244</v>
       </c>
@@ -10700,7 +10700,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="337" spans="1:27" ht="45" x14ac:dyDescent="0.25">
+    <row r="337" spans="1:27" ht="48" x14ac:dyDescent="0.2">
       <c r="A337" s="5" t="s">
         <v>245</v>
       </c>
@@ -10741,7 +10741,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="338" spans="1:27" ht="60" x14ac:dyDescent="0.25">
+    <row r="338" spans="1:27" ht="48" x14ac:dyDescent="0.2">
       <c r="A338" s="5" t="s">
         <v>246</v>
       </c>
@@ -10776,7 +10776,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="339" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="339" spans="1:27" ht="16" x14ac:dyDescent="0.2">
       <c r="A339" s="5" t="s">
         <v>247</v>
       </c>
@@ -10793,7 +10793,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="340" spans="1:27" ht="45" x14ac:dyDescent="0.25">
+    <row r="340" spans="1:27" ht="48" x14ac:dyDescent="0.2">
       <c r="A340" s="5" t="s">
         <v>248</v>
       </c>
@@ -10831,7 +10831,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="341" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="341" spans="1:27" ht="16" x14ac:dyDescent="0.2">
       <c r="A341" s="5" t="s">
         <v>249</v>
       </c>
@@ -10848,7 +10848,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="342" spans="1:27" ht="60" x14ac:dyDescent="0.25">
+    <row r="342" spans="1:27" ht="64" x14ac:dyDescent="0.2">
       <c r="A342" s="5" t="s">
         <v>250</v>
       </c>
@@ -10871,7 +10871,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="343" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="343" spans="1:27" ht="16" x14ac:dyDescent="0.2">
       <c r="A343" s="5" t="s">
         <v>251</v>
       </c>
@@ -10888,7 +10888,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="344" spans="1:27" ht="75" x14ac:dyDescent="0.25">
+    <row r="344" spans="1:27" ht="64" x14ac:dyDescent="0.2">
       <c r="A344" s="5" t="s">
         <v>252</v>
       </c>
@@ -10923,7 +10923,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="345" spans="1:27" ht="45" x14ac:dyDescent="0.25">
+    <row r="345" spans="1:27" ht="48" x14ac:dyDescent="0.2">
       <c r="A345" s="5" t="s">
         <v>253</v>
       </c>
@@ -10952,7 +10952,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="346" spans="1:27" ht="30" x14ac:dyDescent="0.25">
+    <row r="346" spans="1:27" ht="32" x14ac:dyDescent="0.2">
       <c r="A346" s="5" t="s">
         <v>254</v>
       </c>
@@ -10975,7 +10975,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="347" spans="1:27" ht="75" x14ac:dyDescent="0.25">
+    <row r="347" spans="1:27" ht="64" x14ac:dyDescent="0.2">
       <c r="A347" s="5" t="s">
         <v>255</v>
       </c>
@@ -11016,7 +11016,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="348" spans="1:27" ht="30" x14ac:dyDescent="0.25">
+    <row r="348" spans="1:27" ht="32" x14ac:dyDescent="0.2">
       <c r="A348" s="9" t="s">
         <v>256</v>
       </c>
@@ -11039,7 +11039,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="349" spans="1:27" ht="90" x14ac:dyDescent="0.25">
+    <row r="349" spans="1:27" ht="80" x14ac:dyDescent="0.2">
       <c r="A349" s="5" t="s">
         <v>257</v>
       </c>
@@ -11050,7 +11050,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="350" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="350" spans="1:27" ht="16" x14ac:dyDescent="0.2">
       <c r="A350" s="5" t="s">
         <v>258</v>
       </c>
@@ -11061,7 +11061,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="351" spans="1:27" ht="60" x14ac:dyDescent="0.25">
+    <row r="351" spans="1:27" ht="48" x14ac:dyDescent="0.2">
       <c r="A351" s="5" t="s">
         <v>259</v>
       </c>
@@ -11072,7 +11072,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="352" spans="1:27" ht="60" x14ac:dyDescent="0.25">
+    <row r="352" spans="1:27" ht="48" x14ac:dyDescent="0.2">
       <c r="A352" s="5" t="s">
         <v>260</v>
       </c>
@@ -11083,7 +11083,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="353" spans="1:3" ht="60" x14ac:dyDescent="0.25">
+    <row r="353" spans="1:3" ht="48" x14ac:dyDescent="0.2">
       <c r="A353" s="5" t="s">
         <v>259</v>
       </c>
@@ -11094,7 +11094,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="354" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="354" spans="1:3" ht="32" x14ac:dyDescent="0.2">
       <c r="A354" s="5" t="s">
         <v>261</v>
       </c>
@@ -11105,7 +11105,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="355" spans="1:3" ht="75" x14ac:dyDescent="0.25">
+    <row r="355" spans="1:3" ht="64" x14ac:dyDescent="0.2">
       <c r="A355" s="5" t="s">
         <v>262</v>
       </c>
@@ -11116,7 +11116,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="356" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="356" spans="1:3" ht="16" x14ac:dyDescent="0.2">
       <c r="A356" s="5" t="s">
         <v>263</v>
       </c>
@@ -11127,7 +11127,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="357" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+    <row r="357" spans="1:3" ht="32" x14ac:dyDescent="0.2">
       <c r="A357" s="5" t="s">
         <v>264</v>
       </c>
@@ -11138,7 +11138,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="358" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="358" spans="1:3" ht="48" x14ac:dyDescent="0.2">
       <c r="A358" s="5" t="s">
         <v>265</v>
       </c>
@@ -11149,7 +11149,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="359" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+    <row r="359" spans="1:3" ht="32" x14ac:dyDescent="0.2">
       <c r="A359" s="5" t="s">
         <v>266</v>
       </c>
@@ -11160,7 +11160,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="360" spans="1:3" ht="105" x14ac:dyDescent="0.25">
+    <row r="360" spans="1:3" ht="80" x14ac:dyDescent="0.2">
       <c r="A360" s="5" t="s">
         <v>267</v>
       </c>
@@ -11171,7 +11171,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="361" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+    <row r="361" spans="1:3" ht="32" x14ac:dyDescent="0.2">
       <c r="A361" s="5" t="s">
         <v>268</v>
       </c>
@@ -11182,7 +11182,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="362" spans="1:3" ht="60" x14ac:dyDescent="0.25">
+    <row r="362" spans="1:3" ht="64" x14ac:dyDescent="0.2">
       <c r="A362" s="5" t="s">
         <v>269</v>
       </c>
@@ -11193,7 +11193,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="363" spans="1:3" ht="60" x14ac:dyDescent="0.25">
+    <row r="363" spans="1:3" ht="48" x14ac:dyDescent="0.2">
       <c r="A363" s="5" t="s">
         <v>270</v>
       </c>
@@ -11204,7 +11204,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="364" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+    <row r="364" spans="1:3" ht="32" x14ac:dyDescent="0.2">
       <c r="A364" s="5" t="s">
         <v>271</v>
       </c>
@@ -11215,7 +11215,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="365" spans="1:3" ht="120" x14ac:dyDescent="0.25">
+    <row r="365" spans="1:3" ht="96" x14ac:dyDescent="0.2">
       <c r="A365" s="5" t="s">
         <v>272</v>
       </c>
@@ -11226,7 +11226,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="366" spans="1:3" ht="75" x14ac:dyDescent="0.25">
+    <row r="366" spans="1:3" ht="64" x14ac:dyDescent="0.2">
       <c r="A366" s="5" t="s">
         <v>286</v>
       </c>
@@ -11237,7 +11237,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="367" spans="1:3" ht="75" x14ac:dyDescent="0.25">
+    <row r="367" spans="1:3" ht="64" x14ac:dyDescent="0.2">
       <c r="A367" s="5" t="s">
         <v>273</v>
       </c>
@@ -11248,7 +11248,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="368" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="368" spans="1:3" ht="32" x14ac:dyDescent="0.2">
       <c r="A368" s="5" t="s">
         <v>274</v>
       </c>
@@ -11259,7 +11259,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="369" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="369" spans="1:3" ht="16" x14ac:dyDescent="0.2">
       <c r="A369" s="5" t="s">
         <v>275</v>
       </c>
@@ -11270,7 +11270,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="370" spans="1:3" ht="75" x14ac:dyDescent="0.25">
+    <row r="370" spans="1:3" ht="64" x14ac:dyDescent="0.2">
       <c r="A370" s="5" t="s">
         <v>276</v>
       </c>
@@ -11281,7 +11281,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="371" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="371" spans="1:3" ht="32" x14ac:dyDescent="0.2">
       <c r="A371" s="5" t="s">
         <v>277</v>
       </c>
@@ -11292,7 +11292,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="372" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+    <row r="372" spans="1:3" ht="32" x14ac:dyDescent="0.2">
       <c r="A372" s="5" t="s">
         <v>278</v>
       </c>
@@ -11303,7 +11303,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="373" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="373" spans="1:3" ht="48" x14ac:dyDescent="0.2">
       <c r="A373" s="5" t="s">
         <v>279</v>
       </c>
@@ -11314,7 +11314,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="374" spans="1:3" ht="75" x14ac:dyDescent="0.25">
+    <row r="374" spans="1:3" ht="64" x14ac:dyDescent="0.2">
       <c r="A374" s="5" t="s">
         <v>280</v>
       </c>
@@ -11325,7 +11325,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="375" spans="1:3" ht="60" x14ac:dyDescent="0.25">
+    <row r="375" spans="1:3" ht="48" x14ac:dyDescent="0.2">
       <c r="A375" s="5" t="s">
         <v>281</v>
       </c>
@@ -11336,7 +11336,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="376" spans="1:3" ht="120" x14ac:dyDescent="0.25">
+    <row r="376" spans="1:3" ht="96" x14ac:dyDescent="0.2">
       <c r="A376" s="5" t="s">
         <v>282</v>
       </c>
@@ -11347,7 +11347,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="377" spans="1:3" ht="60" x14ac:dyDescent="0.25">
+    <row r="377" spans="1:3" ht="48" x14ac:dyDescent="0.2">
       <c r="A377" s="5" t="s">
         <v>283</v>
       </c>
@@ -11358,7 +11358,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="378" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="378" spans="1:3" ht="32" x14ac:dyDescent="0.2">
       <c r="A378" s="5" t="s">
         <v>284</v>
       </c>
@@ -11369,7 +11369,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="379" spans="1:3" ht="60" x14ac:dyDescent="0.25">
+    <row r="379" spans="1:3" ht="48" x14ac:dyDescent="0.2">
       <c r="A379" s="5" t="s">
         <v>285</v>
       </c>
@@ -11380,7 +11380,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="380" spans="1:3" ht="105" x14ac:dyDescent="0.25">
+    <row r="380" spans="1:3" ht="80" x14ac:dyDescent="0.2">
       <c r="A380" s="5" t="s">
         <v>209</v>
       </c>
@@ -11391,7 +11391,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="381" spans="1:3" ht="180" x14ac:dyDescent="0.25">
+    <row r="381" spans="1:3" ht="160" x14ac:dyDescent="0.2">
       <c r="A381" s="5" t="s">
         <v>210</v>
       </c>
@@ -11402,7 +11402,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="382" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="382" spans="1:3" ht="16" x14ac:dyDescent="0.2">
       <c r="A382" s="5" t="s">
         <v>211</v>
       </c>
@@ -11413,7 +11413,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="383" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+    <row r="383" spans="1:3" ht="32" x14ac:dyDescent="0.2">
       <c r="A383" s="5" t="s">
         <v>212</v>
       </c>
@@ -11424,7 +11424,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="384" spans="1:3" ht="210" x14ac:dyDescent="0.25">
+    <row r="384" spans="1:3" ht="192" x14ac:dyDescent="0.2">
       <c r="A384" s="5" t="s">
         <v>213</v>
       </c>
@@ -11435,7 +11435,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="385" spans="1:3" ht="60" x14ac:dyDescent="0.25">
+    <row r="385" spans="1:3" ht="48" x14ac:dyDescent="0.2">
       <c r="A385" s="5" t="s">
         <v>214</v>
       </c>
@@ -11446,7 +11446,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="386" spans="1:3" ht="300" x14ac:dyDescent="0.25">
+    <row r="386" spans="1:3" ht="272" x14ac:dyDescent="0.2">
       <c r="A386" s="5" t="s">
         <v>215</v>
       </c>
@@ -11457,7 +11457,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="387" spans="1:3" ht="75" x14ac:dyDescent="0.25">
+    <row r="387" spans="1:3" ht="64" x14ac:dyDescent="0.2">
       <c r="A387" s="5" t="s">
         <v>216</v>
       </c>
@@ -11468,7 +11468,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="388" spans="1:3" ht="75" x14ac:dyDescent="0.25">
+    <row r="388" spans="1:3" ht="64" x14ac:dyDescent="0.2">
       <c r="A388" s="5" t="s">
         <v>217</v>
       </c>
@@ -11479,7 +11479,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="389" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+    <row r="389" spans="1:3" ht="32" x14ac:dyDescent="0.2">
       <c r="A389" s="5" t="s">
         <v>218</v>
       </c>
@@ -11490,7 +11490,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="390" spans="1:3" ht="135" x14ac:dyDescent="0.25">
+    <row r="390" spans="1:3" ht="128" x14ac:dyDescent="0.2">
       <c r="A390" s="5" t="s">
         <v>219</v>
       </c>
@@ -11501,7 +11501,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="391" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+    <row r="391" spans="1:3" ht="32" x14ac:dyDescent="0.2">
       <c r="A391" s="5" t="s">
         <v>220</v>
       </c>
@@ -11512,7 +11512,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="392" spans="1:3" ht="105" x14ac:dyDescent="0.25">
+    <row r="392" spans="1:3" ht="96" x14ac:dyDescent="0.2">
       <c r="A392" s="5" t="s">
         <v>221</v>
       </c>
@@ -11523,7 +11523,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="393" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+    <row r="393" spans="1:3" ht="32" x14ac:dyDescent="0.2">
       <c r="A393" s="5" t="s">
         <v>222</v>
       </c>
@@ -11534,7 +11534,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="394" spans="1:3" ht="150" x14ac:dyDescent="0.25">
+    <row r="394" spans="1:3" ht="144" x14ac:dyDescent="0.2">
       <c r="A394" s="5" t="s">
         <v>223</v>
       </c>
@@ -11545,7 +11545,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="395" spans="1:3" ht="90" x14ac:dyDescent="0.25">
+    <row r="395" spans="1:3" ht="80" x14ac:dyDescent="0.2">
       <c r="A395" s="5" t="s">
         <v>224</v>
       </c>
@@ -11556,7 +11556,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="396" spans="1:3" ht="135" x14ac:dyDescent="0.25">
+    <row r="396" spans="1:3" ht="112" x14ac:dyDescent="0.2">
       <c r="A396" s="5" t="s">
         <v>225</v>
       </c>
@@ -11567,7 +11567,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="397" spans="1:3" ht="60" x14ac:dyDescent="0.25">
+    <row r="397" spans="1:3" ht="48" x14ac:dyDescent="0.2">
       <c r="A397" s="5" t="s">
         <v>226</v>
       </c>
@@ -11578,7 +11578,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="398" spans="1:3" ht="195" x14ac:dyDescent="0.25">
+    <row r="398" spans="1:3" ht="176" x14ac:dyDescent="0.2">
       <c r="A398" s="5" t="s">
         <v>227</v>
       </c>
@@ -11589,7 +11589,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="399" spans="1:3" ht="180" x14ac:dyDescent="0.25">
+    <row r="399" spans="1:3" ht="144" x14ac:dyDescent="0.2">
       <c r="A399" s="5" t="s">
         <v>228</v>
       </c>
@@ -11600,7 +11600,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="400" spans="1:3" ht="60" x14ac:dyDescent="0.25">
+    <row r="400" spans="1:3" ht="64" x14ac:dyDescent="0.2">
       <c r="A400" s="5" t="s">
         <v>229</v>
       </c>
@@ -11611,7 +11611,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="401" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="401" spans="1:3" ht="16" x14ac:dyDescent="0.2">
       <c r="A401" s="5" t="s">
         <v>230</v>
       </c>
@@ -11622,7 +11622,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="402" spans="1:3" ht="210" x14ac:dyDescent="0.25">
+    <row r="402" spans="1:3" ht="192" x14ac:dyDescent="0.2">
       <c r="A402" s="5" t="s">
         <v>231</v>
       </c>
@@ -11633,7 +11633,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="403" spans="1:3" ht="60" x14ac:dyDescent="0.25">
+    <row r="403" spans="1:3" ht="48" x14ac:dyDescent="0.2">
       <c r="A403" s="5" t="s">
         <v>232</v>
       </c>
@@ -11644,7 +11644,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="404" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="404" spans="1:3" ht="16" x14ac:dyDescent="0.2">
       <c r="A404" s="5" t="s">
         <v>233</v>
       </c>
@@ -11655,7 +11655,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="405" spans="1:3" ht="255" x14ac:dyDescent="0.25">
+    <row r="405" spans="1:3" ht="240" x14ac:dyDescent="0.2">
       <c r="A405" s="5" t="s">
         <v>234</v>
       </c>
@@ -11666,7 +11666,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="406" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+    <row r="406" spans="1:3" ht="32" x14ac:dyDescent="0.2">
       <c r="A406" s="5" t="s">
         <v>235</v>
       </c>
@@ -11677,7 +11677,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="407" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+    <row r="407" spans="1:3" ht="32" x14ac:dyDescent="0.2">
       <c r="A407" s="5" t="s">
         <v>236</v>
       </c>
@@ -11688,7 +11688,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="408" spans="1:3" ht="105" x14ac:dyDescent="0.25">
+    <row r="408" spans="1:3" ht="96" x14ac:dyDescent="0.2">
       <c r="A408" s="5" t="s">
         <v>237</v>
       </c>
@@ -11699,7 +11699,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="409" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+    <row r="409" spans="1:3" ht="16" x14ac:dyDescent="0.2">
       <c r="A409" s="5" t="s">
         <v>238</v>
       </c>
@@ -11710,7 +11710,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="410" spans="1:3" ht="180" x14ac:dyDescent="0.25">
+    <row r="410" spans="1:3" ht="160" x14ac:dyDescent="0.2">
       <c r="A410" s="5" t="s">
         <v>239</v>
       </c>
@@ -11721,7 +11721,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="411" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+    <row r="411" spans="1:3" ht="32" x14ac:dyDescent="0.2">
       <c r="A411" s="5" t="s">
         <v>240</v>
       </c>
@@ -11732,7 +11732,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="412" spans="1:3" ht="60" x14ac:dyDescent="0.25">
+    <row r="412" spans="1:3" ht="48" x14ac:dyDescent="0.2">
       <c r="A412" s="5" t="s">
         <v>241</v>
       </c>
@@ -11743,7 +11743,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="413" spans="1:3" ht="60" x14ac:dyDescent="0.25">
+    <row r="413" spans="1:3" ht="48" x14ac:dyDescent="0.2">
       <c r="A413" s="5" t="s">
         <v>242</v>
       </c>
@@ -11754,7 +11754,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="414" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="414" spans="1:3" ht="32" x14ac:dyDescent="0.2">
       <c r="A414" s="5" t="s">
         <v>243</v>
       </c>
